--- a/шаблони/комплекти/Стрільби/Шаблон_Роздавально-здавальна відомість.xlsx
+++ b/шаблони/комплекти/Стрільби/Шаблон_Роздавально-здавальна відомість.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>РОЗДАВАЛЬНО-ЗДАВАЛЬНА  ВІДОМІСТЬ №{{номер_відомості}}/      від ___.__.20__ року
+    <x:t>РОЗДАВАЛЬНО-ЗДАВАЛЬНА  ВІДОМІСТЬ №{{номер_відомості}}/      від {{дата}} року
 боєприпасів на пункті бойового постачання ______________________ КППК ______________________ військової  частини {{номер_вч}}
 (підрозділ)
 За {{дата_аркуша}} р.</x:t>
@@ -44,7 +44,7 @@
     <x:t>Примітка</x:t>
   </x:si>
   <x:si>
-    <x:t>(здавальник)</x:t>
+    <x:t>Одержувач (здавальник)</x:t>
   </x:si>
   <x:si>
     <x:t>артпострілів, ПТКР, ракет</x:t>
@@ -86,26 +86,26 @@
     <x:t>шт.</x:t>
   </x:si>
   <x:si>
+    <x:t>{{піб_ініціали}}</x:t>
+  </x:si>
+  <x:si>
     <x:t>{{калібр}}</x:t>
   </x:si>
   <x:si>
+    <x:t>{{кількість_патронів}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{дата_аркуша}}</x:t>
+  </x:si>
+  <x:si>
     <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{піб_ініціали}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{кількість_патронів}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{дата_аркуша}}</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">  Начальник пункту бойового постачання: _{{курсовий_офіцер}}_______________________________________
   Командир підрозділу: _{{звання_підписанта}}________________{{піб_підписанта}}______________________________________________
   Керівник стрільб: _{{керівник_стрільб}}_________________________________________________________________________
   Боєприпаси, їх елементи, стріляні гільзи по роздавально-здавальним відомостям ______/         від 
-  											 і за книгою інв. № ____/___ обліковані
+   і за книгою інв. № ____/___ обліковані
   Комірник складу ЗББ та Р___________________________________________________________________________________________
   “____”_________________20__ р.
   Правильність обліку та розходу перевірив: ____________________________________________________________________________
@@ -707,7 +707,7 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr filterMode="false">
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
-    <x:pageSetUpPr fitToPage="false"/>
+    <x:pageSetUpPr fitToPage="true"/>
   </x:sheetPr>
   <x:dimension ref="A1:Q1048576"/>
   <x:sheetFormatPr defaultColWidth="8.567768" defaultRowHeight="14.25" zeroHeight="false"/>
@@ -964,18 +964,18 @@
     </x:row>
     <x:row r="9" spans="1:17" ht="17.35" customHeight="1">
       <x:c r="A9" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B9" s="16"/>
       <x:c r="C9" s="14"/>
       <x:c r="D9" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="17" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="F9" s="17" t="s">
-        <x:v>24</x:v>
       </x:c>
       <x:c r="G9" s="18"/>
       <x:c r="H9" s="18"/>
@@ -984,13 +984,13 @@
       <x:c r="K9" s="16"/>
       <x:c r="L9" s="18"/>
       <x:c r="M9" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="N9" s="19" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="O9" s="17" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P9" s="18"/>
       <x:c r="Q9" s="5"/>
@@ -1078,7 +1078,7 @@
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="true"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <x:pageSetup paperSize="9" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <x:headerFooter differentOddEven="false" differentFirst="false">
     <x:oddHeader/>
     <x:oddFooter/>

--- a/шаблони/комплекти/Стрільби/Шаблон_Роздавально-здавальна відомість.xlsx
+++ b/шаблони/комплекти/Стрільби/Шаблон_Роздавально-здавальна відомість.xlsx
@@ -23,12 +23,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>РОЗДАВАЛЬНО-ЗДАВАЛЬНА  ВІДОМІСТЬ №{{номер_відомості}}/      від {{дата}} року
-боєприпасів на пункті бойового постачання ______________________ КППК ______________________ військової  частини {{номер_вч}}
-(підрозділ)
-За {{дата_аркуша}} р.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Видано, шт.</x:t>
   </x:si>
   <x:si>
@@ -111,6 +105,12 @@
   Правильність обліку та розходу перевірив: ____________________________________________________________________________
   “____”_________________20__ р.</x:t>
   </x:si>
+  <x:si>
+    <x:t>РОЗДАВАЛЬНО-ЗДАВАЛЬНА  ВІДОМІСТЬ №{{номер_відомості}}/ від {{дата}} року
+боєприпасів на пункті бойового постачання ______________________ КППК ______________________ військової  частини {{номер_вч}}
+(підрозділ)
+За {{дата_аркуша}} р.</x:t>
+  </x:si>
 </x:sst>
 </file>
 
@@ -120,7 +120,7 @@
     <x:numFmt numFmtId="164" formatCode="General"/>
     <x:numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="16">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -220,6 +220,14 @@
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Times New Roman"/>
+      <x:family val="2"/>
+      <x:charset val="204"/>
     </x:font>
   </x:fonts>
   <x:fills count="3">
@@ -315,7 +323,7 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="38">
+  <x:cellStyleXfs count="39">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <x:protection locked="true" hidden="false"/>
@@ -393,8 +401,11 @@
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="15" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <x:protection locked="true" hidden="false"/>
@@ -517,6 +528,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -721,7 +736,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:17" ht="82.5" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -742,16 +757,16 @@
     <x:row r="2" spans="1:17" ht="14.25" customHeight="1">
       <x:c r="A2" s="3"/>
       <x:c r="B2" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="4"/>
       <x:c r="D2" s="4"/>
       <x:c r="E2" s="4"/>
       <x:c r="F2" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="4" t="s">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="s">
-        <x:v>3</x:v>
       </x:c>
       <x:c r="H2" s="4"/>
       <x:c r="I2" s="4"/>
@@ -761,23 +776,23 @@
       <x:c r="M2" s="4"/>
       <x:c r="N2" s="4"/>
       <x:c r="O2" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P2" s="4" t="s">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="P2" s="4" t="s">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="Q2" s="5"/>
     </x:row>
     <x:row r="3" spans="1:17" ht="14.25" customHeight="1">
       <x:c r="A3" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="4"/>
       <x:c r="D3" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E3" s="4"/>
       <x:c r="F3" s="4"/>
@@ -801,19 +816,19 @@
       <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
       <x:c r="G4" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H4" s="3"/>
       <x:c r="I4" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J4" s="4"/>
       <x:c r="K4" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="N4" s="3"/>
       <x:c r="O4" s="4"/>
@@ -823,20 +838,20 @@
     <x:row r="5" spans="1:17" ht="14.25" customHeight="1">
       <x:c r="A5" s="7"/>
       <x:c r="B5" s="8" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C5" s="8" t="s">
+      <x:c r="D5" s="8" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D5" s="8" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E5" s="8" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="9" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H5" s="9"/>
       <x:c r="I5" s="4"/>
@@ -844,7 +859,7 @@
       <x:c r="K5" s="4"/>
       <x:c r="L5" s="4"/>
       <x:c r="M5" s="9" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N5" s="9"/>
       <x:c r="O5" s="4"/>
@@ -859,28 +874,28 @@
       <x:c r="E6" s="8"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="8" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H6" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I6" s="8" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J6" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K6" s="8" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J6" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K6" s="8" t="s">
+      <x:c r="L6" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M6" s="8" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N6" s="8" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="L6" s="10" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="M6" s="8" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="N6" s="8" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="O6" s="4"/>
       <x:c r="P6" s="4"/>
@@ -895,15 +910,15 @@
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="8"/>
       <x:c r="H7" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I7" s="8"/>
       <x:c r="J7" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K7" s="8"/>
       <x:c r="L7" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="M7" s="8"/>
       <x:c r="N7" s="8"/>
@@ -964,18 +979,18 @@
     </x:row>
     <x:row r="9" spans="1:17" ht="17.35" customHeight="1">
       <x:c r="A9" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B9" s="16"/>
       <x:c r="C9" s="14"/>
       <x:c r="D9" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="F9" s="17" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="17" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="G9" s="18"/>
       <x:c r="H9" s="18"/>
@@ -984,20 +999,20 @@
       <x:c r="K9" s="16"/>
       <x:c r="L9" s="18"/>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N9" s="19" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O9" s="17" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="P9" s="18"/>
       <x:c r="Q9" s="5"/>
     </x:row>
     <x:row r="10" spans="1:17" ht="14.25" customHeight="1">
-      <x:c r="A10" s="23" t="s">
-        <x:v>25</x:v>
+      <x:c r="A10" s="31" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="23"/>
       <x:c r="C10" s="23"/>
